--- a/data/50001580- CIA. RIO MINERALES.xlsx
+++ b/data/50001580- CIA. RIO MINERALES.xlsx
@@ -219,9 +219,6 @@
     <t>ot  4379 -  TABLERO YD 63 KW,ot 4379 -  TABLERO YD 63 KW</t>
   </si>
   <si>
-    <t>Tarea en curso</t>
-  </si>
-  <si>
     <t>1216769310026574</t>
   </si>
   <si>
@@ -321,6 +318,9 @@
   </si>
   <si>
     <t>Propuesta compras:,Generación OC corte laser  OT4378</t>
+  </si>
+  <si>
+    <t>Tarea en curso</t>
   </si>
   <si>
     <t>1216788054986657</t>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="C9" s="10"/>
       <c r="D9" s="9">
-        <v>46274.7341921412</v>
+        <v>46279.74439658565</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>45</v>
@@ -2122,9 +2122,11 @@
       <c r="B11" s="9">
         <v>46225.58274704861</v>
       </c>
-      <c r="C11" s="10"/>
+      <c r="C11" s="9">
+        <v>46279.74438925926</v>
+      </c>
       <c r="D11" s="9">
-        <v>46274.73486938658</v>
+        <v>46279.74565146991</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>54</v>
@@ -2172,25 +2174,27 @@
         <v>33</v>
       </c>
       <c r="T11" s="10">
-        <v>0.2</v>
-      </c>
-      <c r="U11" s="12" t="s">
-        <v>58</v>
+        <v>1</v>
+      </c>
+      <c r="U11" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B12" s="5">
         <v>46225.59567834491</v>
       </c>
-      <c r="C12" s="6"/>
+      <c r="C12" s="5">
+        <v>46279.74448738426</v>
+      </c>
       <c r="D12" s="5">
-        <v>46225.612248819445</v>
+        <v>46279.744488888886</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>26</v>
@@ -2220,10 +2224,10 @@
         <v>54</v>
       </c>
       <c r="O12" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="P12" s="6" t="s">
         <v>61</v>
-      </c>
-      <c r="P12" s="6" t="s">
-        <v>62</v>
       </c>
       <c r="Q12" s="6"/>
       <c r="R12" s="6"/>
@@ -2233,17 +2237,19 @@
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B13" s="9">
         <v>46225.595835520835</v>
       </c>
-      <c r="C13" s="10"/>
+      <c r="C13" s="9">
+        <v>46279.74457292824</v>
+      </c>
       <c r="D13" s="9">
-        <v>46225.61224515046</v>
+        <v>46279.74457475694</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F13" s="10" t="s">
         <v>26</v>
@@ -2273,10 +2279,10 @@
         <v>54</v>
       </c>
       <c r="O13" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="P13" s="10" t="s">
         <v>61</v>
-      </c>
-      <c r="P13" s="10" t="s">
-        <v>62</v>
       </c>
       <c r="Q13" s="10"/>
       <c r="R13" s="10"/>
@@ -2286,7 +2292,7 @@
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B14" s="5">
         <v>46225.58085679398</v>
@@ -2298,7 +2304,7 @@
         <v>46226.576112442126</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>25</v>
@@ -2322,7 +2328,7 @@
         <v>26</v>
       </c>
       <c r="O14" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="P14" s="6" t="s">
         <v>26</v>
@@ -2339,7 +2345,7 @@
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B15" s="9">
         <v>46225.58095215278</v>
@@ -2351,7 +2357,7 @@
         <v>46228.19449930555</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F15" s="10" t="s">
         <v>26</v>
@@ -2372,19 +2378,19 @@
         <v>26</v>
       </c>
       <c r="L15" s="10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="M15" s="10" t="s">
         <v>26</v>
       </c>
       <c r="N15" s="10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="O15" s="10" t="s">
         <v>38</v>
       </c>
       <c r="P15" s="10" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Q15" s="9">
         <v>46227</v>
@@ -2404,7 +2410,7 @@
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B16" s="5">
         <v>46225.580861423616</v>
@@ -2414,7 +2420,7 @@
         <v>46225.59611458333</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>25</v>
@@ -2438,7 +2444,7 @@
         <v>26</v>
       </c>
       <c r="O16" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="P16" s="6" t="s">
         <v>26</v>
@@ -2451,7 +2457,7 @@
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B17" s="9">
         <v>46225.580958923616</v>
@@ -2461,16 +2467,16 @@
         <v>46237.5500087963</v>
       </c>
       <c r="E17" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="F17" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G17" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="F17" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G17" s="10" t="s">
+      <c r="H17" s="10" t="s">
         <v>76</v>
-      </c>
-      <c r="H17" s="10" t="s">
-        <v>77</v>
       </c>
       <c r="I17" s="9">
         <v>46226</v>
@@ -2488,13 +2494,13 @@
         <v>26</v>
       </c>
       <c r="N17" s="10" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="O17" s="10" t="s">
         <v>38</v>
       </c>
       <c r="P17" s="10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="Q17" s="9">
         <v>46227</v>
@@ -2514,7 +2520,7 @@
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B18" s="5">
         <v>46225.58096494213</v>
@@ -2524,16 +2530,16 @@
         <v>46237.550030706014</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G18" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="H18" s="6" t="s">
         <v>76</v>
-      </c>
-      <c r="H18" s="6" t="s">
-        <v>77</v>
       </c>
       <c r="I18" s="5">
         <v>46226</v>
@@ -2551,13 +2557,13 @@
         <v>26</v>
       </c>
       <c r="N18" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="O18" s="6" t="s">
         <v>38</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="Q18" s="5">
         <v>46227</v>
@@ -2577,7 +2583,7 @@
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B19" s="9">
         <v>46225.58097109954</v>
@@ -2587,16 +2593,16 @@
         <v>46237.55005269676</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F19" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G19" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="H19" s="10" t="s">
         <v>76</v>
-      </c>
-      <c r="H19" s="10" t="s">
-        <v>77</v>
       </c>
       <c r="I19" s="9">
         <v>46226</v>
@@ -2614,13 +2620,13 @@
         <v>26</v>
       </c>
       <c r="N19" s="10" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="O19" s="10" t="s">
         <v>38</v>
       </c>
       <c r="P19" s="10" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Q19" s="9">
         <v>46227</v>
@@ -2640,7 +2646,7 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B20" s="5">
         <v>46225.58086628473</v>
@@ -2650,7 +2656,7 @@
         <v>46225.59619578704</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>25</v>
@@ -2674,7 +2680,7 @@
         <v>26</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="P20" s="6" t="s">
         <v>26</v>
@@ -2687,7 +2693,7 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B21" s="9">
         <v>46225.580978240745</v>
@@ -2697,16 +2703,16 @@
         <v>46247.17789210648</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F21" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G21" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="H21" s="10" t="s">
         <v>76</v>
-      </c>
-      <c r="H21" s="10" t="s">
-        <v>77</v>
       </c>
       <c r="I21" s="9">
         <v>46245</v>
@@ -2724,13 +2730,13 @@
         <v>26</v>
       </c>
       <c r="N21" s="10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="O21" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="P21" s="10" t="s">
         <v>89</v>
-      </c>
-      <c r="P21" s="10" t="s">
-        <v>90</v>
       </c>
       <c r="Q21" s="9">
         <v>46246</v>
@@ -2745,7 +2751,7 @@
         <v>0</v>
       </c>
       <c r="U21" s="12" t="s">
-        <v>58</v>
+        <v>90</v>
       </c>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
@@ -2766,10 +2772,10 @@
         <v>26</v>
       </c>
       <c r="G22" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="H22" s="6" t="s">
         <v>76</v>
-      </c>
-      <c r="H22" s="6" t="s">
-        <v>77</v>
       </c>
       <c r="I22" s="5">
         <v>46245</v>
@@ -2787,10 +2793,10 @@
         <v>26</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="P22" s="6" t="s">
         <v>93</v>
@@ -2808,7 +2814,7 @@
         <v>0</v>
       </c>
       <c r="U22" s="12" t="s">
-        <v>58</v>
+        <v>90</v>
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
@@ -2829,10 +2835,10 @@
         <v>26</v>
       </c>
       <c r="G23" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="H23" s="10" t="s">
         <v>76</v>
-      </c>
-      <c r="H23" s="10" t="s">
-        <v>77</v>
       </c>
       <c r="I23" s="9">
         <v>46245</v>
@@ -2850,10 +2856,10 @@
         <v>26</v>
       </c>
       <c r="N23" s="10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="O23" s="10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="P23" s="10" t="s">
         <v>96</v>
@@ -2871,7 +2877,7 @@
         <v>0</v>
       </c>
       <c r="U23" s="12" t="s">
-        <v>58</v>
+        <v>90</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
@@ -2892,10 +2898,10 @@
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="H24" s="6" t="s">
         <v>76</v>
-      </c>
-      <c r="H24" s="6" t="s">
-        <v>77</v>
       </c>
       <c r="I24" s="5">
         <v>46245</v>
@@ -2913,10 +2919,10 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="P24" s="6" t="s">
         <v>99</v>
@@ -2934,7 +2940,7 @@
         <v>0</v>
       </c>
       <c r="U24" s="12" t="s">
-        <v>58</v>
+        <v>90</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
@@ -2955,10 +2961,10 @@
         <v>26</v>
       </c>
       <c r="G25" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="H25" s="10" t="s">
         <v>76</v>
-      </c>
-      <c r="H25" s="10" t="s">
-        <v>77</v>
       </c>
       <c r="I25" s="9">
         <v>46231</v>
@@ -2976,7 +2982,7 @@
         <v>26</v>
       </c>
       <c r="N25" s="10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="O25" s="10" t="s">
         <v>48</v>
@@ -3152,7 +3158,7 @@
         <v>106</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="P28" s="6" t="s">
         <v>113</v>
@@ -4048,7 +4054,7 @@
         <v>160</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="P44" s="6" t="s">
         <v>166</v>
@@ -4148,7 +4154,7 @@
         <v>46245.1918381713</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
@@ -5326,7 +5332,7 @@
         <v>228</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="P66" s="6" t="s">
         <v>232</v>
@@ -5389,7 +5395,7 @@
         <v>228</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="P67" s="10" t="s">
         <v>235</v>
@@ -5452,7 +5458,7 @@
         <v>228</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="P68" s="6" t="s">
         <v>232</v>
@@ -5485,7 +5491,7 @@
         <v>46225.61467041667</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
@@ -5601,10 +5607,10 @@
         <v>26</v>
       </c>
       <c r="G71" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="H71" s="10" t="s">
         <v>76</v>
-      </c>
-      <c r="H71" s="10" t="s">
-        <v>77</v>
       </c>
       <c r="I71" s="9">
         <v>46275</v>
@@ -5664,10 +5670,10 @@
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="H72" s="6" t="s">
         <v>76</v>
-      </c>
-      <c r="H72" s="6" t="s">
-        <v>77</v>
       </c>
       <c r="I72" s="5">
         <v>46275</v>
@@ -5717,10 +5723,10 @@
         <v>26</v>
       </c>
       <c r="G73" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="H73" s="10" t="s">
         <v>76</v>
-      </c>
-      <c r="H73" s="10" t="s">
-        <v>77</v>
       </c>
       <c r="I73" s="9">
         <v>46275</v>
@@ -5761,7 +5767,7 @@
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46232.62438234954</v>
+        <v>46279.139763263884</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>251</v>
@@ -5770,10 +5776,10 @@
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="H74" s="6" t="s">
         <v>76</v>
-      </c>
-      <c r="H74" s="6" t="s">
-        <v>77</v>
       </c>
       <c r="I74" s="5">
         <v>46286</v>
@@ -5805,8 +5811,8 @@
       <c r="R74" s="5">
         <v>46286</v>
       </c>
-      <c r="S74" s="7" t="s">
-        <v>33</v>
+      <c r="S74" s="12" t="s">
+        <v>245</v>
       </c>
       <c r="T74" s="6">
         <v>0</v>
@@ -5833,10 +5839,10 @@
         <v>26</v>
       </c>
       <c r="G75" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="H75" s="10" t="s">
         <v>76</v>
-      </c>
-      <c r="H75" s="10" t="s">
-        <v>77</v>
       </c>
       <c r="I75" s="9">
         <v>46286</v>
@@ -5886,10 +5892,10 @@
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="H76" s="6" t="s">
         <v>76</v>
-      </c>
-      <c r="H76" s="6" t="s">
-        <v>77</v>
       </c>
       <c r="I76" s="5">
         <v>46286</v>
@@ -5939,10 +5945,10 @@
         <v>26</v>
       </c>
       <c r="G77" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="H77" s="10" t="s">
         <v>76</v>
-      </c>
-      <c r="H77" s="10" t="s">
-        <v>77</v>
       </c>
       <c r="I77" s="9">
         <v>46287</v>
@@ -6002,10 +6008,10 @@
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="H78" s="6" t="s">
         <v>76</v>
-      </c>
-      <c r="H78" s="6" t="s">
-        <v>77</v>
       </c>
       <c r="I78" s="6"/>
       <c r="J78" s="5">
@@ -6053,10 +6059,10 @@
         <v>26</v>
       </c>
       <c r="G79" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="H79" s="10" t="s">
         <v>76</v>
-      </c>
-      <c r="H79" s="10" t="s">
-        <v>77</v>
       </c>
       <c r="I79" s="10"/>
       <c r="J79" s="9">
@@ -6104,10 +6110,10 @@
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="H80" s="6" t="s">
         <v>76</v>
-      </c>
-      <c r="H80" s="6" t="s">
-        <v>77</v>
       </c>
       <c r="I80" s="5">
         <v>46288</v>
@@ -6167,10 +6173,10 @@
         <v>26</v>
       </c>
       <c r="G81" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="H81" s="10" t="s">
         <v>76</v>
-      </c>
-      <c r="H81" s="10" t="s">
-        <v>77</v>
       </c>
       <c r="I81" s="9">
         <v>46288</v>
@@ -6220,10 +6226,10 @@
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="H82" s="6" t="s">
         <v>76</v>
-      </c>
-      <c r="H82" s="6" t="s">
-        <v>77</v>
       </c>
       <c r="I82" s="5">
         <v>46288</v>
@@ -6273,10 +6279,10 @@
         <v>26</v>
       </c>
       <c r="G83" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="H83" s="10" t="s">
         <v>76</v>
-      </c>
-      <c r="H83" s="10" t="s">
-        <v>77</v>
       </c>
       <c r="I83" s="9">
         <v>46289</v>
@@ -6326,10 +6332,10 @@
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="H84" s="6" t="s">
         <v>76</v>
-      </c>
-      <c r="H84" s="6" t="s">
-        <v>77</v>
       </c>
       <c r="I84" s="5">
         <v>46290</v>
@@ -6389,10 +6395,10 @@
         <v>26</v>
       </c>
       <c r="G85" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="H85" s="10" t="s">
         <v>76</v>
-      </c>
-      <c r="H85" s="10" t="s">
-        <v>77</v>
       </c>
       <c r="I85" s="10"/>
       <c r="J85" s="9">
@@ -6440,10 +6446,10 @@
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="H86" s="6" t="s">
         <v>76</v>
-      </c>
-      <c r="H86" s="6" t="s">
-        <v>77</v>
       </c>
       <c r="I86" s="6"/>
       <c r="J86" s="5">
@@ -6491,10 +6497,10 @@
         <v>26</v>
       </c>
       <c r="G87" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="H87" s="10" t="s">
         <v>76</v>
-      </c>
-      <c r="H87" s="10" t="s">
-        <v>77</v>
       </c>
       <c r="I87" s="9">
         <v>46293</v>
@@ -6554,10 +6560,10 @@
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="H88" s="6" t="s">
         <v>76</v>
-      </c>
-      <c r="H88" s="6" t="s">
-        <v>77</v>
       </c>
       <c r="I88" s="5">
         <v>46293</v>
@@ -6607,10 +6613,10 @@
         <v>26</v>
       </c>
       <c r="G89" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="H89" s="10" t="s">
         <v>76</v>
-      </c>
-      <c r="H89" s="10" t="s">
-        <v>77</v>
       </c>
       <c r="I89" s="9">
         <v>46293</v>
@@ -6865,7 +6871,7 @@
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46225.61577960648</v>
+        <v>46279.7444940162</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>303</v>
@@ -6896,7 +6902,7 @@
         <v>294</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="P94" s="6" t="s">
         <v>304</v>
@@ -6916,7 +6922,7 @@
       </c>
       <c r="C95" s="10"/>
       <c r="D95" s="9">
-        <v>46225.61577443287</v>
+        <v>46279.74458172453</v>
       </c>
       <c r="E95" s="10" t="s">
         <v>303</v>
@@ -6947,7 +6953,7 @@
         <v>294</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="P95" s="10" t="s">
         <v>304</v>
@@ -6976,10 +6982,10 @@
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="H96" s="6" t="s">
         <v>76</v>
-      </c>
-      <c r="H96" s="6" t="s">
-        <v>77</v>
       </c>
       <c r="I96" s="6"/>
       <c r="J96" s="5">
@@ -7037,10 +7043,10 @@
         <v>26</v>
       </c>
       <c r="G97" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="H97" s="10" t="s">
         <v>76</v>
-      </c>
-      <c r="H97" s="10" t="s">
-        <v>77</v>
       </c>
       <c r="I97" s="9">
         <v>46302</v>
@@ -7090,10 +7096,10 @@
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="H98" s="6" t="s">
         <v>76</v>
-      </c>
-      <c r="H98" s="6" t="s">
-        <v>77</v>
       </c>
       <c r="I98" s="5">
         <v>46302</v>
@@ -7143,10 +7149,10 @@
         <v>26</v>
       </c>
       <c r="G99" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="H99" s="10" t="s">
         <v>76</v>
-      </c>
-      <c r="H99" s="10" t="s">
-        <v>77</v>
       </c>
       <c r="I99" s="9">
         <v>46302</v>
@@ -7196,10 +7202,10 @@
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="H100" s="6" t="s">
         <v>76</v>
-      </c>
-      <c r="H100" s="6" t="s">
-        <v>77</v>
       </c>
       <c r="I100" s="5">
         <v>46302</v>

--- a/data/50001580- CIA. RIO MINERALES.xlsx
+++ b/data/50001580- CIA. RIO MINERALES.xlsx
@@ -5936,7 +5936,7 @@
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="9">
-        <v>46232.624382071765</v>
+        <v>46280.165977847224</v>
       </c>
       <c r="E77" s="10" t="s">
         <v>259</v>
@@ -5980,8 +5980,8 @@
       <c r="R77" s="9">
         <v>46287</v>
       </c>
-      <c r="S77" s="7" t="s">
-        <v>33</v>
+      <c r="S77" s="12" t="s">
+        <v>245</v>
       </c>
       <c r="T77" s="10">
         <v>0</v>

--- a/data/50001580- CIA. RIO MINERALES.xlsx
+++ b/data/50001580- CIA. RIO MINERALES.xlsx
@@ -5598,7 +5598,7 @@
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="9">
-        <v>46274.139942662034</v>
+        <v>46281.25046357639</v>
       </c>
       <c r="E71" s="10" t="s">
         <v>243</v>
@@ -5661,7 +5661,7 @@
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46225.61483068287</v>
+        <v>46281.250461400465</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>180</v>
@@ -5714,7 +5714,7 @@
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="9">
-        <v>46225.61482673611</v>
+        <v>46281.25046246528</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>180</v>
@@ -6101,7 +6101,7 @@
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46232.624381828704</v>
+        <v>46281.13377107639</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>267</v>
@@ -6145,8 +6145,8 @@
       <c r="R80" s="5">
         <v>46288</v>
       </c>
-      <c r="S80" s="7" t="s">
-        <v>33</v>
+      <c r="S80" s="12" t="s">
+        <v>245</v>
       </c>
       <c r="T80" s="6">
         <v>0</v>

--- a/data/50001580- CIA. RIO MINERALES.xlsx
+++ b/data/50001580- CIA. RIO MINERALES.xlsx
@@ -464,6 +464,9 @@
     <t>Generacion Oc  OT4378,Armado OT4378,Control de calidad  OT4378</t>
   </si>
   <si>
+    <t>Media</t>
+  </si>
+  <si>
     <t>1216788147871096</t>
   </si>
   <si>
@@ -783,9 +786,6 @@
   </si>
   <si>
     <t>Montaje:,Montaje Alabe OT4378</t>
-  </si>
-  <si>
-    <t>Media</t>
   </si>
   <si>
     <t>1216788148296193</t>
@@ -3581,7 +3581,7 @@
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="5">
-        <v>46225.61316422454</v>
+        <v>46282.125953229166</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>134</v>
@@ -3625,8 +3625,8 @@
       <c r="R36" s="5">
         <v>46247</v>
       </c>
-      <c r="S36" s="7" t="s">
-        <v>33</v>
+      <c r="S36" s="12" t="s">
+        <v>138</v>
       </c>
       <c r="T36" s="6">
         <v>0</v>
@@ -3637,7 +3637,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B37" s="9">
         <v>46225.58109630787</v>
@@ -3647,7 +3647,7 @@
         <v>46255.62865305555</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>26</v>
@@ -3677,10 +3677,10 @@
         <v>134</v>
       </c>
       <c r="O37" s="10" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="P37" s="10" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="Q37" s="10"/>
       <c r="R37" s="10"/>
@@ -3690,7 +3690,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B38" s="5">
         <v>46225.58110178241</v>
@@ -3700,7 +3700,7 @@
         <v>46225.613047719904</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
@@ -3730,10 +3730,10 @@
         <v>134</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -3743,7 +3743,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B39" s="9">
         <v>46225.58110600694</v>
@@ -3753,16 +3753,16 @@
         <v>46225.613129363424</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F39" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I39" s="9">
         <v>46289</v>
@@ -3783,7 +3783,7 @@
         <v>134</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="P39" s="10" t="s">
         <v>134</v>
@@ -3796,7 +3796,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B40" s="5">
         <v>46225.59682005787</v>
@@ -3806,16 +3806,16 @@
         <v>46225.6133383912</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="I40" s="5">
         <v>46233</v>
@@ -3836,7 +3836,7 @@
         <v>105</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="P40" s="6" t="s">
         <v>26</v>
@@ -3859,7 +3859,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B41" s="9">
         <v>46225.59686481481</v>
@@ -3875,10 +3875,10 @@
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="I41" s="9">
         <v>46233</v>
@@ -3896,13 +3896,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O41" s="10" t="s">
         <v>101</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q41" s="10"/>
       <c r="R41" s="10"/>
@@ -3912,7 +3912,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B42" s="5">
         <v>46225.59692966435</v>
@@ -3922,16 +3922,16 @@
         <v>46225.613310636574</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="I42" s="5">
         <v>46244</v>
@@ -3949,13 +3949,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O42" s="6" t="s">
         <v>102</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q42" s="6"/>
       <c r="R42" s="6"/>
@@ -3965,7 +3965,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B43" s="9">
         <v>46225.58111748843</v>
@@ -3975,7 +3975,7 @@
         <v>46238.48696734954</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>25</v>
@@ -3999,7 +3999,7 @@
         <v>26</v>
       </c>
       <c r="O43" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="P43" s="10" t="s">
         <v>26</v>
@@ -4012,7 +4012,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B44" s="5">
         <v>46225.58112127315</v>
@@ -4024,16 +4024,16 @@
         <v>46235.20153063658</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I44" s="5">
         <v>46230</v>
@@ -4051,13 +4051,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O44" s="6" t="s">
         <v>66</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q44" s="5">
         <v>46234</v>
@@ -4077,7 +4077,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B45" s="9">
         <v>46225.58112643519</v>
@@ -4089,16 +4089,16 @@
         <v>46242.202891875</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="I45" s="9">
         <v>46237</v>
@@ -4116,13 +4116,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q45" s="9">
         <v>46241</v>
@@ -4142,7 +4142,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B46" s="5">
         <v>46225.58113097222</v>
@@ -4160,10 +4160,10 @@
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I46" s="5">
         <v>46244</v>
@@ -4181,13 +4181,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q46" s="5">
         <v>46244</v>
@@ -4207,7 +4207,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B47" s="9">
         <v>46225.58114445602</v>
@@ -4217,16 +4217,16 @@
         <v>46225.61347256944</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I47" s="9">
         <v>46290</v>
@@ -4244,13 +4244,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O47" s="10" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="P47" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q47" s="9">
         <v>46290</v>
@@ -4270,7 +4270,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B48" s="5">
         <v>46225.58114871528</v>
@@ -4280,16 +4280,16 @@
         <v>46225.61551950232</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I48" s="5">
         <v>46290</v>
@@ -4307,13 +4307,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q48" s="6"/>
       <c r="R48" s="6"/>
@@ -4323,7 +4323,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B49" s="9">
         <v>46225.58115283565</v>
@@ -4333,16 +4333,16 @@
         <v>46225.615519513885</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H49" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I49" s="9">
         <v>46290</v>
@@ -4360,13 +4360,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P49" s="10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q49" s="10"/>
       <c r="R49" s="10"/>
@@ -4376,7 +4376,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B50" s="5">
         <v>46225.581171631944</v>
@@ -4386,7 +4386,7 @@
         <v>46225.59181146991</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>25</v>
@@ -4410,7 +4410,7 @@
         <v>26</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4423,7 +4423,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B51" s="9">
         <v>46225.58117489584</v>
@@ -4433,16 +4433,16 @@
         <v>46261.17149666666</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I51" s="9">
         <v>46260</v>
@@ -4460,13 +4460,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="O51" s="10" t="s">
         <v>115</v>
       </c>
       <c r="P51" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q51" s="9">
         <v>46260</v>
@@ -4486,7 +4486,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B52" s="5">
         <v>46225.58118028935</v>
@@ -4496,16 +4496,16 @@
         <v>46261.17149707176</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I52" s="5">
         <v>46260</v>
@@ -4523,13 +4523,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="O52" s="6" t="s">
         <v>123</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q52" s="5">
         <v>46260</v>
@@ -4549,7 +4549,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B53" s="9">
         <v>46225.58118576389</v>
@@ -4559,16 +4559,16 @@
         <v>46261.17149663194</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H53" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I53" s="9">
         <v>46260</v>
@@ -4586,13 +4586,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="O53" s="10" t="s">
         <v>131</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q53" s="9">
         <v>46260</v>
@@ -4612,7 +4612,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B54" s="5">
         <v>46225.58119107639</v>
@@ -4622,16 +4622,16 @@
         <v>46262.17656298611</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I54" s="5">
         <v>46261</v>
@@ -4649,13 +4649,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q54" s="5">
         <v>46261</v>
@@ -4675,7 +4675,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B55" s="9">
         <v>46225.58119642361</v>
@@ -4685,16 +4685,16 @@
         <v>46262.1765628125</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H55" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I55" s="9">
         <v>46261</v>
@@ -4712,13 +4712,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q55" s="9">
         <v>46261</v>
@@ -4738,7 +4738,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B56" s="5">
         <v>46225.581201678244</v>
@@ -4748,16 +4748,16 @@
         <v>46262.17656298611</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I56" s="5">
         <v>46261</v>
@@ -4775,13 +4775,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q56" s="5">
         <v>46261</v>
@@ -4801,7 +4801,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B57" s="9">
         <v>46225.58120702546</v>
@@ -4811,7 +4811,7 @@
         <v>46225.59190644676</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>25</v>
@@ -4835,7 +4835,7 @@
         <v>26</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="P57" s="10" t="s">
         <v>26</v>
@@ -4848,7 +4848,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B58" s="5">
         <v>46225.58121010417</v>
@@ -4864,10 +4864,10 @@
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="I58" s="5">
         <v>46262</v>
@@ -4885,13 +4885,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="O58" s="6" t="s">
         <v>95</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q58" s="5">
         <v>46266</v>
@@ -4911,7 +4911,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B59" s="9">
         <v>46225.581215474536</v>
@@ -4921,16 +4921,16 @@
         <v>46274.1467808912</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H59" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="I59" s="9">
         <v>46267</v>
@@ -4948,13 +4948,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q59" s="9">
         <v>46273</v>
@@ -4974,7 +4974,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B60" s="5">
         <v>46225.581219618056</v>
@@ -4984,16 +4984,16 @@
         <v>46273.16871085648</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="I60" s="5">
         <v>46267</v>
@@ -5011,13 +5011,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q60" s="6"/>
       <c r="R60" s="6"/>
@@ -5027,7 +5027,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B61" s="9">
         <v>46225.58123596065</v>
@@ -5037,16 +5037,16 @@
         <v>46273.16871189815</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H61" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="I61" s="9">
         <v>46267</v>
@@ -5064,13 +5064,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="P61" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q61" s="10"/>
       <c r="R61" s="10"/>
@@ -5080,7 +5080,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B62" s="5">
         <v>46225.58129219907</v>
@@ -5090,16 +5090,16 @@
         <v>46275.15575423611</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I62" s="5">
         <v>46274</v>
@@ -5117,13 +5117,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q62" s="5">
         <v>46274</v>
@@ -5143,7 +5143,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B63" s="9">
         <v>46225.58129802083</v>
@@ -5153,16 +5153,16 @@
         <v>46274.168634444446</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I63" s="10"/>
       <c r="J63" s="9">
@@ -5178,13 +5178,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="P63" s="10" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q63" s="10"/>
       <c r="R63" s="10"/>
@@ -5194,7 +5194,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B64" s="5">
         <v>46225.581304374995</v>
@@ -5204,16 +5204,16 @@
         <v>46274.168635671296</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I64" s="6"/>
       <c r="J64" s="5">
@@ -5229,13 +5229,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5245,7 +5245,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B65" s="9">
         <v>46225.58131015046</v>
@@ -5255,7 +5255,7 @@
         <v>46225.59759329861</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>25</v>
@@ -5279,7 +5279,7 @@
         <v>26</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="P65" s="10" t="s">
         <v>26</v>
@@ -5292,7 +5292,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B66" s="5">
         <v>46225.58131376158</v>
@@ -5302,16 +5302,16 @@
         <v>46232.18544357639</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I66" s="5">
         <v>46230</v>
@@ -5329,13 +5329,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="O66" s="6" t="s">
         <v>74</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q66" s="5">
         <v>46231</v>
@@ -5355,7 +5355,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B67" s="9">
         <v>46225.58131929398</v>
@@ -5365,16 +5365,16 @@
         <v>46232.18544451389</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H67" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I67" s="9">
         <v>46230</v>
@@ -5392,13 +5392,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="O67" s="10" t="s">
         <v>79</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q67" s="9">
         <v>46231</v>
@@ -5418,7 +5418,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B68" s="5">
         <v>46225.58132505787</v>
@@ -5428,16 +5428,16 @@
         <v>46232.18544357639</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I68" s="5">
         <v>46230</v>
@@ -5455,13 +5455,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="O68" s="6" t="s">
         <v>82</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q68" s="5">
         <v>46231</v>
@@ -5481,7 +5481,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B69" s="9">
         <v>46225.597591134254</v>
@@ -5497,10 +5497,10 @@
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H69" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I69" s="9">
         <v>46293</v>
@@ -5518,10 +5518,10 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P69" s="10" t="s">
         <v>57</v>
@@ -5544,7 +5544,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B70" s="5">
         <v>46225.58133054398</v>
@@ -5554,7 +5554,7 @@
         <v>46232.67654627315</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>25</v>
@@ -5578,7 +5578,7 @@
         <v>26</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>26</v>
@@ -5591,17 +5591,17 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B71" s="9">
         <v>46225.58133395833</v>
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="9">
-        <v>46281.25046357639</v>
+        <v>46282.16223802083</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>26</v>
@@ -5628,13 +5628,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q71" s="9">
         <v>46281</v>
@@ -5642,8 +5642,8 @@
       <c r="R71" s="9">
         <v>46275</v>
       </c>
-      <c r="S71" s="12" t="s">
-        <v>245</v>
+      <c r="S71" s="11" t="s">
+        <v>52</v>
       </c>
       <c r="T71" s="10">
         <v>0</v>
@@ -5664,7 +5664,7 @@
         <v>46281.250461400465</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
@@ -5691,10 +5691,10 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P72" s="6" t="s">
         <v>247</v>
@@ -5717,7 +5717,7 @@
         <v>46281.25046246528</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
@@ -5744,10 +5744,10 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P73" s="10" t="s">
         <v>249</v>
@@ -5797,7 +5797,7 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="O74" s="6" t="s">
         <v>252</v>
@@ -5812,7 +5812,7 @@
         <v>46286</v>
       </c>
       <c r="S74" s="12" t="s">
-        <v>245</v>
+        <v>138</v>
       </c>
       <c r="T74" s="6">
         <v>0</v>
@@ -5833,7 +5833,7 @@
         <v>46238.48696328704</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
@@ -5886,7 +5886,7 @@
         <v>46238.486963877316</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
@@ -5966,7 +5966,7 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="O77" s="10" t="s">
         <v>260</v>
@@ -5981,7 +5981,7 @@
         <v>46287</v>
       </c>
       <c r="S77" s="12" t="s">
-        <v>245</v>
+        <v>138</v>
       </c>
       <c r="T77" s="10">
         <v>0</v>
@@ -6002,7 +6002,7 @@
         <v>46225.61518142361</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
@@ -6053,7 +6053,7 @@
         <v>46225.615182291665</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
@@ -6131,7 +6131,7 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="O80" s="6" t="s">
         <v>268</v>
@@ -6146,7 +6146,7 @@
         <v>46288</v>
       </c>
       <c r="S80" s="12" t="s">
-        <v>245</v>
+        <v>138</v>
       </c>
       <c r="T80" s="6">
         <v>0</v>
@@ -6167,7 +6167,7 @@
         <v>46238.48696648148</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
@@ -6220,7 +6220,7 @@
         <v>46238.48696707176</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
@@ -6300,7 +6300,7 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="O83" s="10" t="s">
         <v>267</v>
@@ -6323,7 +6323,7 @@
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46232.62438278935</v>
+        <v>46282.12595271991</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>277</v>
@@ -6353,7 +6353,7 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="O84" s="6" t="s">
         <v>279</v>
@@ -6367,8 +6367,8 @@
       <c r="R84" s="5">
         <v>46289</v>
       </c>
-      <c r="S84" s="7" t="s">
-        <v>33</v>
+      <c r="S84" s="12" t="s">
+        <v>138</v>
       </c>
       <c r="T84" s="6">
         <v>0</v>
@@ -6389,7 +6389,7 @@
         <v>46225.61551967592</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
@@ -6440,7 +6440,7 @@
         <v>46225.61552056713</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6518,7 +6518,7 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="O87" s="10" t="s">
         <v>286</v>
@@ -6554,7 +6554,7 @@
         <v>46225.61568175926</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
@@ -6584,7 +6584,7 @@
         <v>280</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P88" s="6" t="s">
         <v>288</v>
@@ -6607,7 +6607,7 @@
         <v>46225.615682592594</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
@@ -6637,7 +6637,7 @@
         <v>280</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P89" s="10" t="s">
         <v>288</v>
@@ -6770,7 +6770,7 @@
         <v>46225.61578579861</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
@@ -6798,7 +6798,7 @@
         <v>294</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P92" s="6" t="s">
         <v>300</v>
@@ -6821,7 +6821,7 @@
         <v>46225.61578274306</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
@@ -6851,7 +6851,7 @@
         <v>294</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P93" s="10" t="s">
         <v>300</v>
@@ -7037,7 +7037,7 @@
         <v>46225.615894421295</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
@@ -7067,7 +7067,7 @@
         <v>307</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P97" s="10" t="s">
         <v>310</v>
@@ -7090,7 +7090,7 @@
         <v>46225.61589104167</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
@@ -7120,7 +7120,7 @@
         <v>307</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P98" s="6" t="s">
         <v>310</v>
@@ -7255,10 +7255,10 @@
         <v>26</v>
       </c>
       <c r="G101" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H101" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="I101" s="9">
         <v>46303</v>
@@ -7312,16 +7312,16 @@
         <v>46225.61600570602</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="I102" s="6"/>
       <c r="J102" s="5">
@@ -7340,7 +7340,7 @@
         <v>316</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P102" s="6" t="s">
         <v>318</v>
@@ -7363,16 +7363,16 @@
         <v>46225.61600274306</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G103" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H103" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="I103" s="10"/>
       <c r="J103" s="9">
@@ -7391,7 +7391,7 @@
         <v>316</v>
       </c>
       <c r="O103" s="10" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P103" s="10" t="s">
         <v>318</v>
@@ -7420,10 +7420,10 @@
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="I104" s="5">
         <v>46303</v>
@@ -7473,10 +7473,10 @@
         <v>26</v>
       </c>
       <c r="G105" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H105" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="I105" s="9">
         <v>46303</v>
@@ -7526,10 +7526,10 @@
         <v>26</v>
       </c>
       <c r="G106" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="I106" s="5">
         <v>46304</v>
@@ -7583,16 +7583,16 @@
         <v>46225.61621090278</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F107" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G107" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H107" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="I107" s="10"/>
       <c r="J107" s="9">
@@ -7611,7 +7611,7 @@
         <v>324</v>
       </c>
       <c r="O107" s="10" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P107" s="10" t="s">
         <v>327</v>
@@ -7634,16 +7634,16 @@
         <v>46225.61620709491</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G108" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H108" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="I108" s="6"/>
       <c r="J108" s="5">
@@ -7662,7 +7662,7 @@
         <v>324</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P108" s="6" t="s">
         <v>327</v>
@@ -7691,10 +7691,10 @@
         <v>26</v>
       </c>
       <c r="G109" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H109" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="I109" s="9">
         <v>46304</v>
@@ -7744,10 +7744,10 @@
         <v>26</v>
       </c>
       <c r="G110" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H110" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="I110" s="5">
         <v>46304</v>

--- a/data/50001580- CIA. RIO MINERALES.xlsx
+++ b/data/50001580- CIA. RIO MINERALES.xlsx
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="5">
-        <v>46225.6133383912</v>
+        <v>46283.14044724537</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>151</v>
@@ -3847,8 +3847,8 @@
       <c r="R40" s="5">
         <v>46233</v>
       </c>
-      <c r="S40" s="7" t="s">
-        <v>33</v>
+      <c r="S40" s="12" t="s">
+        <v>138</v>
       </c>
       <c r="T40" s="6">
         <v>0</v>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="C47" s="10"/>
       <c r="D47" s="9">
-        <v>46225.61347256944</v>
+        <v>46283.140456863424</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>176</v>
@@ -4258,8 +4258,8 @@
       <c r="R47" s="9">
         <v>46290</v>
       </c>
-      <c r="S47" s="7" t="s">
-        <v>33</v>
+      <c r="S47" s="12" t="s">
+        <v>138</v>
       </c>
       <c r="T47" s="10">
         <v>0</v>

--- a/data/50001580- CIA. RIO MINERALES.xlsx
+++ b/data/50001580- CIA. RIO MINERALES.xlsx
@@ -1703,7 +1703,7 @@
         <v>46226.57179957176</v>
       </c>
       <c r="D4" s="5">
-        <v>46226.57181140046</v>
+        <v>46284.36262428241</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -2126,7 +2126,7 @@
         <v>46279.74438925926</v>
       </c>
       <c r="D11" s="9">
-        <v>46279.74565146991</v>
+        <v>46284.35669247685</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>54</v>
@@ -2301,7 +2301,7 @@
         <v>46226.57610013889</v>
       </c>
       <c r="D14" s="5">
-        <v>46226.576112442126</v>
+        <v>46284.35677775463</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>65</v>
@@ -2417,7 +2417,7 @@
       </c>
       <c r="C16" s="6"/>
       <c r="D16" s="5">
-        <v>46225.59611458333</v>
+        <v>46284.35678138889</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>71</v>
@@ -3412,7 +3412,7 @@
       </c>
       <c r="C33" s="10"/>
       <c r="D33" s="9">
-        <v>46260.17450096065</v>
+        <v>46284.36358049768</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>126</v>
